--- a/data/gravel/Nehaus Hummingbird Core (short) 2025.xlsx
+++ b/data/gravel/Nehaus Hummingbird Core (short) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23ED6E68-2D94-4241-8DBE-C1182FEE7982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC018ADA-D58B-5B4B-9A26-A4978B6F4C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32440" yWindow="-23980" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="121">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,24 @@
   </si>
   <si>
     <t>a8:g33</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -754,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1500,163 +1518,193 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52">
-        <v>31.6</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62" s="3"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="3"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B68" s="3"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="3"/>
+        <v>55</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70">
-        <v>1399</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="3">
-        <f>B70+1999</f>
-        <v>3398</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B71" s="3"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>64</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B72" s="3"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>76</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B73" s="3"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="3"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="3"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76">
+        <v>1399</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="3">
+        <f>B76+1999</f>
+        <v>3398</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>69</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>112</v>
       </c>
     </row>

--- a/data/gravel/Nehaus Hummingbird Core (short) 2025.xlsx
+++ b/data/gravel/Nehaus Hummingbird Core (short) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC018ADA-D58B-5B4B-9A26-A4978B6F4C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A684835-AB1D-7F4B-BC07-959149CBE16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32440" yWindow="-23980" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -344,9 +344,6 @@
     <t>steerer_min</t>
   </si>
   <si>
-    <t>travel</t>
-  </si>
-  <si>
     <t>rigid 120 Fox 34</t>
   </si>
   <si>
@@ -377,9 +374,6 @@
     <t>Hummingbird Core (short)</t>
   </si>
   <si>
-    <t>a8:g33</t>
-  </si>
-  <si>
     <t>head_tube_d</t>
   </si>
   <si>
@@ -396,6 +390,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:g34</t>
   </si>
 </sst>
 </file>
@@ -772,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -791,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -815,12 +818,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -828,7 +831,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1152,7 +1155,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>99</v>
@@ -1206,7 +1209,7 @@
         <v>44</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1231,260 +1234,258 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="A25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" s="3"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>20</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="G27" s="4"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="F28" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29">
-        <v>700</v>
-      </c>
-      <c r="D29">
-        <v>700</v>
-      </c>
-      <c r="E29">
-        <v>700</v>
-      </c>
-      <c r="F29">
-        <v>700</v>
-      </c>
-      <c r="G29">
-        <v>700</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="D30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="E30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="F30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
       <c r="G30">
-        <v>2.4</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C31">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D31">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E31">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="F31">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G31">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32">
+        <v>2.6</v>
+      </c>
+      <c r="D32">
+        <v>2.6</v>
+      </c>
+      <c r="E32">
+        <v>2.6</v>
+      </c>
+      <c r="F32">
+        <v>2.6</v>
+      </c>
+      <c r="G32">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>27</v>
       </c>
-      <c r="C32">
-        <f>C34*2.54</f>
+      <c r="C33">
+        <f>C35*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D32">
-        <f t="shared" ref="D32:G33" si="2">D34*2.54</f>
+      <c r="D33">
+        <f t="shared" ref="D33:G34" si="2">D35*2.54</f>
         <v>170.18</v>
       </c>
-      <c r="E32">
+      <c r="E33">
         <f t="shared" si="2"/>
         <v>175.26</v>
       </c>
-      <c r="F32">
+      <c r="F33">
         <f t="shared" si="2"/>
         <v>180.34</v>
       </c>
-      <c r="G32">
+      <c r="G33">
         <f t="shared" si="2"/>
         <v>185.42000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>28</v>
       </c>
-      <c r="C33">
-        <f>C35*2.54</f>
+      <c r="C34">
+        <f>C36*2.54</f>
         <v>170.18</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <f t="shared" si="2"/>
         <v>175.26</v>
       </c>
-      <c r="E33">
+      <c r="E34">
         <f t="shared" si="2"/>
         <v>180.34</v>
       </c>
-      <c r="F33">
+      <c r="F34">
         <f t="shared" si="2"/>
         <v>185.42000000000002</v>
       </c>
-      <c r="G33">
+      <c r="G34">
         <f t="shared" si="2"/>
         <v>190.5</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C34">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C35">
         <v>64</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <v>67</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <v>69</v>
       </c>
-      <c r="F34">
+      <c r="F35">
         <v>71</v>
       </c>
-      <c r="G34">
+      <c r="G35">
         <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C35">
-        <v>67</v>
-      </c>
-      <c r="D35">
-        <v>69</v>
-      </c>
-      <c r="E35">
-        <v>71</v>
-      </c>
-      <c r="F35">
-        <v>73</v>
-      </c>
-      <c r="G35">
-        <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H36" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36">
+        <v>67</v>
+      </c>
+      <c r="D36">
+        <v>69</v>
+      </c>
+      <c r="E36">
+        <v>71</v>
+      </c>
+      <c r="F36">
+        <v>73</v>
+      </c>
+      <c r="G36">
+        <v>75</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="H37" s="2"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42">
-        <v>2.6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="B43">
+        <v>2.6</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44">
-        <v>120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45">
         <v>120</v>
@@ -1492,220 +1493,228 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="B46">
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48">
-        <v>148</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49">
-        <v>110</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>41</v>
+      </c>
+      <c r="B50">
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58">
-        <v>31.6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>51</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>54</v>
-      </c>
-      <c r="B68" s="3"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>55</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B69" s="3"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>57</v>
-      </c>
-      <c r="B71" s="3"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B72" s="3"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B73" s="3"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B74" s="3"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B75" s="3"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76">
-        <v>1399</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>107</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B76" s="3"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="3">
-        <f>B76+1999</f>
-        <v>3398</v>
+        <v>62</v>
+      </c>
+      <c r="B77">
+        <v>1399</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="B78" s="3">
+        <f>B77+1999</f>
+        <v>3398</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>65</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>112</v>
+      <c r="B81" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Nehaus Hummingbird Core (short) 2025.xlsx
+++ b/data/gravel/Nehaus Hummingbird Core (short) 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A684835-AB1D-7F4B-BC07-959149CBE16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA533551-6CC2-6E40-A71E-988A7CA56CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -399,6 +399,9 @@
   </si>
   <si>
     <t>a8:g34</t>
+  </si>
+  <si>
+    <t>https://bikepacking.com/bikes/neuhaus-hummingbird-review/</t>
   </si>
 </sst>
 </file>
@@ -1269,7 +1272,12 @@
       <c r="A29" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="6"/>
+      <c r="F29" s="6">
+        <v>2820</v>
+      </c>
+      <c r="H29" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
